--- a/src/attributions/attributions_saliency_traj_317.xlsx
+++ b/src/attributions/attributions_saliency_traj_317.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG5"/>
+  <dimension ref="A1:GG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02733747102320194</v>
+        <v>0.05345336347818375</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1993739604949951</v>
+        <v>0.3003292679786682</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02616443671286106</v>
+        <v>0.02402876503765583</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0702783390879631</v>
+        <v>0.2072489410638809</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01418162137269974</v>
+        <v>0.09928900003433228</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04348403587937355</v>
+        <v>0.1444825381040573</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01158393546938896</v>
+        <v>0.1135070323944092</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001738849096000195</v>
+        <v>0.04994912818074226</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01351279299706221</v>
+        <v>0.03618703782558441</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004828657489269972</v>
+        <v>0.004777416586875916</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1618916690349579</v>
+        <v>0.3369596302509308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001254833652637899</v>
+        <v>0.06209658831357956</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05971120670437813</v>
+        <v>0.2462922632694244</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007314071524888277</v>
+        <v>0.1401067227125168</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0131966033950448</v>
+        <v>0.1094807088375092</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004670766182243824</v>
+        <v>0.06180442124605179</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01536955684423447</v>
+        <v>0.02688844315707684</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01707750372588634</v>
+        <v>0.01885911077260971</v>
       </c>
       <c r="S2" t="n">
-        <v>0.006428624968975782</v>
+        <v>0.01989676803350449</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01416045054793358</v>
+        <v>0.001407383009791374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01756582222878933</v>
+        <v>0.04563864693045616</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02478708140552044</v>
+        <v>0.03168562799692154</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0174082238227129</v>
+        <v>0.009228551760315895</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02133524790406227</v>
+        <v>0.1304073631763458</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001982032554224133</v>
+        <v>0.01253153663128614</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0212969034910202</v>
+        <v>0.01343776006251574</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007943388074636459</v>
+        <v>0.04772846400737762</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02183312550187111</v>
+        <v>0.02954945340752602</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.008092316798865795</v>
+        <v>0.01638012379407883</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.03562136739492416</v>
+        <v>0.04173843562602997</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.02617316320538521</v>
+        <v>0.09329956769943237</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.004305518232285976</v>
+        <v>0.02579929493367672</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.01543444022536278</v>
+        <v>0.08785795420408249</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.008597162552177906</v>
+        <v>0.05550827458500862</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.003000006079673767</v>
+        <v>0.001376674044877291</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01671427488327026</v>
+        <v>0.01649616286158562</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01183532830327749</v>
+        <v>0.03638619557023048</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02245968766510487</v>
+        <v>0.04460185766220093</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.004751185420900583</v>
+        <v>0.02552676200866699</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0004055378376506269</v>
+        <v>0.08154848217964172</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0001683633308857679</v>
+        <v>0.05959578603506088</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0173754021525383</v>
+        <v>0.08397892862558365</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0004444794030860066</v>
+        <v>0.02586075477302074</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01563872769474983</v>
+        <v>0.003951662220060825</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0118379183113575</v>
+        <v>0.03025188110768795</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01760271564126015</v>
+        <v>0.008674813434481621</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.090536929666996</v>
+        <v>0.138571709394455</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.01862319186329842</v>
+        <v>0.004945419728755951</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.02777765318751335</v>
+        <v>0.07588528096675873</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03718170523643494</v>
+        <v>0.1278530657291412</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.01039480697363615</v>
+        <v>0.1126636639237404</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.001503163017332554</v>
+        <v>0.003204661887139082</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.006569250486791134</v>
+        <v>0.01299924124032259</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.008647393435239792</v>
+        <v>0.002153103239834309</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.001384876668453217</v>
+        <v>0.005094127263873816</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.05075875297188759</v>
+        <v>0.09344857931137085</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.02386496961116791</v>
+        <v>0.02723314240574837</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.01162551529705524</v>
+        <v>0.01862082071602345</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01026095077395439</v>
+        <v>0.05693482980132103</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.001469017937779427</v>
+        <v>0.04149316251277924</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.01641861349344254</v>
+        <v>0.01521673519164324</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0004083993844687939</v>
+        <v>0.03442137315869331</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.009393520653247833</v>
+        <v>0.05866857618093491</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.005775338970124722</v>
+        <v>0.05651511624455452</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01341641414910555</v>
+        <v>0.01843303069472313</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.007600280456244946</v>
+        <v>0.002733831293880939</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01846588589251041</v>
+        <v>0.0281903613358736</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.01461133640259504</v>
+        <v>0.06449854373931885</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.02035575360059738</v>
+        <v>0.008504375815391541</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.009443811140954494</v>
+        <v>0.03663229942321777</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.00140154454857111</v>
+        <v>0.04514114558696747</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.007541351020336151</v>
+        <v>0.001624799100682139</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.02829473093152046</v>
+        <v>0.01118753291666508</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.06268146634101868</v>
+        <v>0.06359778344631195</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.01083428878337145</v>
+        <v>0.04846680164337158</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02755966410040855</v>
+        <v>0.05923429131507874</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.007390968501567841</v>
+        <v>0.02729648910462856</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.01726437918841839</v>
+        <v>0.1326701641082764</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.001170595409348607</v>
+        <v>0.01424601208418608</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.01331128552556038</v>
+        <v>0.00774274580180645</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.02061082795262337</v>
+        <v>0.05744756758213043</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.003925581928342581</v>
+        <v>0.03345515951514244</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03071880340576172</v>
+        <v>0.08800493180751801</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.004142946097999811</v>
+        <v>0.008669226430356503</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01630369201302528</v>
+        <v>0.08209189027547836</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.003605354577302933</v>
+        <v>0.01772262528538704</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.007918634451925755</v>
+        <v>0.008646712638437748</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.005276503041386604</v>
+        <v>0.002869384363293648</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.002079178113490343</v>
+        <v>0.03252236172556877</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.009539692662656307</v>
+        <v>0.006872660480439663</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.006169428117573261</v>
+        <v>0.02844397351145744</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.002403288381174207</v>
+        <v>0.07209116220474243</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.005432974081486464</v>
+        <v>0.06582890450954437</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.007767891045659781</v>
+        <v>0.08997657895088196</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.007778478786349297</v>
+        <v>0.06828416883945465</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.03058147616684437</v>
+        <v>0.06514780968427658</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.01130580343306065</v>
+        <v>0.07186830043792725</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.01250972226262093</v>
+        <v>0.05792169272899628</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0009589907713234425</v>
+        <v>0.03295727446675301</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.001883517135865986</v>
+        <v>0.02069390565156937</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.03226879239082336</v>
+        <v>0.07438123971223831</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01222419086843729</v>
+        <v>0.00449276901781559</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.01702451333403587</v>
+        <v>0.08303450793027878</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.005694325547665358</v>
+        <v>0.01872565038502216</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.00717791635543108</v>
+        <v>0.01337248738855124</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0009043603204190731</v>
+        <v>0.002125946804881096</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.003334634238854051</v>
+        <v>0.03371798247098923</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.006814149674028158</v>
+        <v>0.01279756147414446</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001221777871251106</v>
+        <v>0.01730239763855934</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.07645691186189651</v>
+        <v>0.09439896792173386</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.00999565701931715</v>
+        <v>0.0052312221378088</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.08077740669250488</v>
+        <v>0.01596022769808769</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02800302766263485</v>
+        <v>0.01624158769845963</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.01345620211213827</v>
+        <v>0.06099970638751984</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.02816469594836235</v>
+        <v>0.01051664352416992</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.001613994827494025</v>
+        <v>0.1322677582502365</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.001888175029307604</v>
+        <v>0.002016977639868855</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.02187719568610191</v>
+        <v>0.02231541834771633</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02529360167682171</v>
+        <v>0.002795433159917593</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.01285548321902752</v>
+        <v>0.01124192960560322</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.02736078202724457</v>
+        <v>0.05827830731868744</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.02823559194803238</v>
+        <v>0.02237493358552456</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.005756234750151634</v>
+        <v>0.01218517310917377</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.003320037852972746</v>
+        <v>0.03450464829802513</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.00306182075291872</v>
+        <v>0.03014705330133438</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.008909208700060844</v>
+        <v>0.08434239029884338</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.004778253380209208</v>
+        <v>0.02934306114912033</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.01305853109806776</v>
+        <v>0.05866639688611031</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.005974414758384228</v>
+        <v>0.01406416576355696</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.01964063756167889</v>
+        <v>0.01354671642184258</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.01604392006993294</v>
+        <v>0.02681984566152096</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.01129601802676916</v>
+        <v>0.01498101651668549</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.007896756753325462</v>
+        <v>0.007699280045926571</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.02130368165671825</v>
+        <v>0.1193732395768166</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.01457502134144306</v>
+        <v>0.03215429931879044</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.008163304999470711</v>
+        <v>0.05153817310929298</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.02398014813661575</v>
+        <v>0.108120396733284</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.01608736626803875</v>
+        <v>0.0001229085028171539</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.001240956480614841</v>
+        <v>0.06543111056089401</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.01180057041347027</v>
+        <v>0.07685830444097519</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.006206792313605547</v>
+        <v>0.0181952603161335</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001454304321669042</v>
+        <v>0.007597886025905609</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.002925141481682658</v>
+        <v>0.01670227944850922</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.005732065998017788</v>
+        <v>0.02466239035129547</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.002427953528240323</v>
+        <v>0.01964866183698177</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.01114180590957403</v>
+        <v>0.006798043847084045</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.02201723679900169</v>
+        <v>0.007437471766024828</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.01095061097294092</v>
+        <v>0.07214076071977615</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.008212961256504059</v>
+        <v>0.04528678208589554</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.04856828972697258</v>
+        <v>0.03965311124920845</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.007118582725524902</v>
+        <v>0.04669202119112015</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.01572569459676743</v>
+        <v>0.02878689579665661</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.02066975086927414</v>
+        <v>0.06354094296693802</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.00137028656899929</v>
+        <v>0.03257706016302109</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.03474069759249687</v>
+        <v>0.09454575926065445</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.008995706215500832</v>
+        <v>0.01036763936281204</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0171689260751009</v>
+        <v>0.09201250970363617</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.008499489165842533</v>
+        <v>0.01124504022300243</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.008852737955749035</v>
+        <v>0.02294459193944931</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.007396504282951355</v>
+        <v>0.01097186468541622</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.005597037263214588</v>
+        <v>0.03988964483141899</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.009747979231178761</v>
+        <v>0.009187428280711174</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0003872965462505817</v>
+        <v>0.02078414708375931</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01452070940285921</v>
+        <v>0.05404531210660934</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.01317374873906374</v>
+        <v>0.005000318866223097</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.00468277744948864</v>
+        <v>0.02876594103872776</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.007940690033137798</v>
+        <v>0.05093616619706154</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.007151846773922443</v>
+        <v>0.06391031295061111</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.005910438019782305</v>
+        <v>0.02229361981153488</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.003974263090640306</v>
+        <v>0.0223736260086298</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.02015861310064793</v>
+        <v>0.05954660847783089</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.001113711856305599</v>
+        <v>0.03466145321726799</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.03307146951556206</v>
+        <v>0.01030994765460491</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.03979002684354782</v>
+        <v>0.06855039298534393</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.008900300599634647</v>
+        <v>0.04480313509702682</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01769210770726204</v>
+        <v>0.0842181071639061</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.04092278704047203</v>
+        <v>0.08821294456720352</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.01406106352806091</v>
+        <v>0.02439569495618343</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.00238567590713501</v>
+        <v>0.01196941547095776</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.01350283063948154</v>
+        <v>0.02639342471957207</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.001143143279477954</v>
+        <v>0.01945864409208298</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01456711813807487</v>
+        <v>0.0418783500790596</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.01192072872072458</v>
+        <v>0.04328082501888275</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.01283716317266226</v>
+        <v>0.07090473175048828</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.04984039068222046</v>
+        <v>0.02101537212729454</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.02078971639275551</v>
+        <v>0.04783259704709053</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.02836302109062672</v>
+        <v>0.09849999845027924</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.01379978097975254</v>
+        <v>0.03288965672254562</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.004931272473186255</v>
+        <v>0.01254241075366735</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,2847 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001185253844596446</v>
+        <v>0.2150106579065323</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003070324892178178</v>
+        <v>0.4878779053688049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000207196018891409</v>
+        <v>0.062692791223526</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001819415716454387</v>
+        <v>0.2707747519016266</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007835582364350557</v>
+        <v>0.3832707107067108</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003838528355117887</v>
+        <v>0.4885333776473999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000197996327187866</v>
+        <v>0.07076143473386765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003879123250953853</v>
+        <v>0.1446516960859299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001762021129252389</v>
+        <v>0.5034345388412476</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0005532253999263048</v>
+        <v>0.1956299692392349</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002373175928369164</v>
+        <v>0.5620623230934143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006193300941959023</v>
+        <v>0.06542377918958664</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001600513467565179</v>
+        <v>0.2930204272270203</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0008930705371312797</v>
+        <v>0.1601270437240601</v>
       </c>
       <c r="O5" t="n">
-        <v>8.055408397922292e-05</v>
+        <v>0.6435582041740417</v>
       </c>
       <c r="P5" t="n">
-        <v>4.962470848113298e-05</v>
+        <v>0.04425919055938721</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003553825663402677</v>
+        <v>0.01846838183701038</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002654974232427776</v>
+        <v>0.4849022328853607</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003779483959078789</v>
+        <v>0.04578561335802078</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001167319423984736</v>
+        <v>0.0002869516611099243</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0006358554819598794</v>
+        <v>0.08598676323890686</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006881948793306947</v>
+        <v>0.05857350677251816</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0008610642980784178</v>
+        <v>0.1055102497339249</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002137879637302831</v>
+        <v>0.387127697467804</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000282353488728404</v>
+        <v>0.1021205335855484</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0004107192507945001</v>
+        <v>0.0364016629755497</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.295226219459437e-05</v>
+        <v>0.121990792453289</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000267365510808304</v>
+        <v>0.207948699593544</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.738708958029747e-05</v>
+        <v>0.07697153836488724</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0003740469692274928</v>
+        <v>0.02912154234945774</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0009485709015280008</v>
+        <v>0.2652378678321838</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.000319296756060794</v>
+        <v>0.1893373727798462</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.885758532211185e-05</v>
+        <v>0.1475972682237625</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0001133192417910323</v>
+        <v>0.1507685631513596</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.283925303141586e-05</v>
+        <v>0.02883601561188698</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0004904355155304074</v>
+        <v>0.01010031998157501</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0005306651582941413</v>
+        <v>0.02255494892597198</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0003429069765843451</v>
+        <v>0.1766116768121719</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0005141057190485299</v>
+        <v>0.08497330546379089</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.739625966176391e-06</v>
+        <v>0.1173540577292442</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001080006695701741</v>
+        <v>0.1093998551368713</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0005512760835699737</v>
+        <v>0.04583672434091568</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.774095628410578e-05</v>
+        <v>0.0443849116563797</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0006544393836520612</v>
+        <v>0.04152124747633934</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.02963271678891e-05</v>
+        <v>0.1105164065957069</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0007258101832121611</v>
+        <v>0.1787010282278061</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001694318372756243</v>
+        <v>0.08729541301727295</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.000178219546796754</v>
+        <v>0.04795326292514801</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0003439976135268807</v>
+        <v>0.2534835338592529</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0005765149835497141</v>
+        <v>0.3399761617183685</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.683910083258525e-05</v>
+        <v>0.3529571294784546</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.626569226384163e-05</v>
+        <v>0.07325424998998642</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0005021888064220548</v>
+        <v>0.1343623548746109</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.069658775231801e-05</v>
+        <v>0.2867154181003571</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0002308612165506929</v>
+        <v>0.08118600398302078</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0009711573366075754</v>
+        <v>0.2502888441085815</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.493975474266335e-05</v>
+        <v>0.1493358314037323</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.00110540515743196</v>
+        <v>0.02322962321341038</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0007589497836306691</v>
+        <v>0.2758934795856476</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0001130781456595287</v>
+        <v>0.181820809841156</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0001786806096788496</v>
+        <v>0.01217831671237946</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0002262906200485304</v>
+        <v>0.2751281261444092</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.260595233063214e-06</v>
+        <v>0.1088993474841118</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0001141998145612888</v>
+        <v>0.01774688065052032</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0001287478371523321</v>
+        <v>0.2292103171348572</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0001269889035029337</v>
+        <v>0.1338678300380707</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0008897205698303878</v>
+        <v>0.1738207936286926</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0001379388995701447</v>
+        <v>0.04649120941758156</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0004990622401237488</v>
+        <v>0.01412476226687431</v>
       </c>
       <c r="BR5" t="n">
-        <v>5.520139529835433e-05</v>
+        <v>0.03390691056847572</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0003501110186334699</v>
+        <v>0.100864551961422</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0002332694130018353</v>
+        <v>0.02112357690930367</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0008765206439420581</v>
+        <v>0.0681532621383667</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001218692865222692</v>
+        <v>0.01603290438652039</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0002220987807959318</v>
+        <v>0.07318289577960968</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0005526682361960411</v>
+        <v>0.170104518532753</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.112738654133864e-05</v>
+        <v>0.05228396877646446</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0005764152156189084</v>
+        <v>0.3078542351722717</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.182022970169783e-05</v>
+        <v>0.06865596771240234</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001102303649531677</v>
+        <v>0.04069843143224716</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0003959815367124975</v>
+        <v>0.242900550365448</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.149815792217851e-05</v>
+        <v>5.754828453063965e-05</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0004244328301865608</v>
+        <v>0.2035812437534332</v>
       </c>
       <c r="CF5" t="n">
-        <v>1.340282778983237e-05</v>
+        <v>0.0597197636961937</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.000506369979120791</v>
+        <v>0.1213783994317055</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.991755021270365e-05</v>
+        <v>0.007468968629837036</v>
       </c>
       <c r="CI5" t="n">
-        <v>6.820357157266699e-06</v>
+        <v>0.05842307955026627</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0001609956962056458</v>
+        <v>0.002706218510866165</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0001274792739422992</v>
+        <v>0.0544343888759613</v>
       </c>
       <c r="CL5" t="n">
-        <v>9.866555774351582e-05</v>
+        <v>0.05484676361083984</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0002621176827233285</v>
+        <v>0.04826431721448898</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0003083583724219352</v>
+        <v>0.05495643615722656</v>
       </c>
       <c r="CO5" t="n">
-        <v>4.34577523265034e-05</v>
+        <v>0.3489636182785034</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0009960227180272341</v>
+        <v>0.248543381690979</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0005439873784780502</v>
+        <v>0.2766074240207672</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0006720480741932988</v>
+        <v>0.1287590265274048</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.000516991363838315</v>
+        <v>0.05716969817876816</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0005770629504695535</v>
+        <v>0.1077556386590004</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0002350772119825706</v>
+        <v>0.006773838773369789</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.054395397659391e-05</v>
+        <v>0.01255087181925774</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0003386717289686203</v>
+        <v>0.1520413607358932</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0001142941764555871</v>
+        <v>0.06438488513231277</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.000474871281767264</v>
+        <v>0.1151522994041443</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001434025180060416</v>
+        <v>0.001997420564293861</v>
       </c>
       <c r="DA5" t="n">
-        <v>5.735171362175606e-05</v>
+        <v>0.1143016368150711</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001227949251187965</v>
+        <v>0.001119427382946014</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.822396163537633e-05</v>
+        <v>0.02601276151835918</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.565031197969802e-05</v>
+        <v>0.06815562397241592</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0002473637869115919</v>
+        <v>0.04721614718437195</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001981575274839997</v>
+        <v>0.01476997137069702</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0007214704528450966</v>
+        <v>0.2621272504329681</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.001401277258992195</v>
+        <v>0.06137433648109436</v>
       </c>
       <c r="DI5" t="n">
-        <v>3.206785913789645e-05</v>
+        <v>0.3081278800964355</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.000794075895100832</v>
+        <v>0.1990132629871368</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0003837745753116906</v>
+        <v>0.04062362760305405</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.280525339097949e-07</v>
+        <v>0.01882397942245007</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0003320814284961671</v>
+        <v>0.1224672570824623</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0005038387607783079</v>
+        <v>0.002523161470890045</v>
       </c>
       <c r="DO5" t="n">
-        <v>5.240406972006895e-05</v>
+        <v>0.1633510589599609</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001996138016693294</v>
+        <v>0.1293164640665054</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0008137834956869483</v>
+        <v>0.2471925616264343</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0001988979784073308</v>
+        <v>0.1298348754644394</v>
       </c>
       <c r="DS5" t="n">
-        <v>9.522194159217179e-05</v>
+        <v>0.1013564020395279</v>
       </c>
       <c r="DT5" t="n">
-        <v>9.279426740249619e-05</v>
+        <v>0.1229675188660622</v>
       </c>
       <c r="DU5" t="n">
-        <v>2.945285450550728e-05</v>
+        <v>0.07706031948328018</v>
       </c>
       <c r="DV5" t="n">
-        <v>3.353136344230734e-05</v>
+        <v>0.04421553015708923</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0002590394287835807</v>
+        <v>0.1121931970119476</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0002881252148654312</v>
+        <v>0.04657906666398048</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0006403420702554286</v>
+        <v>0.3718553781509399</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0003800053091254085</v>
+        <v>0.09587208181619644</v>
       </c>
       <c r="EA5" t="n">
-        <v>5.152994708623737e-05</v>
+        <v>0.02848989516496658</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0002403255348326638</v>
+        <v>0.0125993974506855</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.582323941169307e-05</v>
+        <v>0.05376085638999939</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0005614386172965169</v>
+        <v>0.1436184793710709</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0004004212678410113</v>
+        <v>0.1560750901699066</v>
       </c>
       <c r="EF5" t="n">
-        <v>2.786407276289538e-05</v>
+        <v>0.03544598072767258</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003798060934059322</v>
+        <v>0.166754350066185</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0003158235922455788</v>
+        <v>0.01657487079501152</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0002672208938747644</v>
+        <v>0.01834385097026825</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0003028964274562895</v>
+        <v>0.0343153178691864</v>
       </c>
       <c r="EK5" t="n">
-        <v>3.017525523318909e-05</v>
+        <v>0.09037965536117554</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.000125720223877579</v>
+        <v>0.005090447142720222</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0001690437202341855</v>
+        <v>0.01343492604792118</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.138507195719285e-05</v>
+        <v>0.07600191235542297</v>
       </c>
       <c r="EO5" t="n">
-        <v>5.060535477241501e-05</v>
+        <v>0.05732838436961174</v>
       </c>
       <c r="EP5" t="n">
-        <v>4.696422547567636e-05</v>
+        <v>0.06206794828176498</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0003557548334356397</v>
+        <v>0.1121207624673843</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0007872724090702832</v>
+        <v>0.1506119966506958</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0001364841591566801</v>
+        <v>0.1897488832473755</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0008921092376112938</v>
+        <v>0.05266882479190826</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0003444715403020382</v>
+        <v>0.1024395301938057</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0007857682066969573</v>
+        <v>0.03763491660356522</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0003143110079690814</v>
+        <v>0.02931839413940907</v>
       </c>
       <c r="EX5" t="n">
-        <v>4.940957296639681e-06</v>
+        <v>0.02429692074656487</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0004387787193991244</v>
+        <v>0.1795332133769989</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001253904774785042</v>
+        <v>0.08605390787124634</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0005310060223564506</v>
+        <v>0.1356781721115112</v>
       </c>
       <c r="FB5" t="n">
-        <v>8.928910392569378e-05</v>
+        <v>0.07418935745954514</v>
       </c>
       <c r="FC5" t="n">
-        <v>6.009899152559228e-06</v>
+        <v>0.09349322319030762</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0003021832380909473</v>
+        <v>0.0255559179931879</v>
       </c>
       <c r="FE5" t="n">
-        <v>9.644167585065588e-05</v>
+        <v>0.06516817212104797</v>
       </c>
       <c r="FF5" t="n">
-        <v>4.320679363445379e-05</v>
+        <v>0.0734555572271347</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002183547912864015</v>
+        <v>0.02575004287064075</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0004570137243717909</v>
+        <v>0.0394652783870697</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0005161400185897946</v>
+        <v>0.1829349398612976</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0001805266656447202</v>
+        <v>0.03775669261813164</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0001017523900372908</v>
+        <v>0.1100741773843765</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0003114248102065176</v>
+        <v>0.1430081427097321</v>
       </c>
       <c r="FM5" t="n">
-        <v>3.064734119107015e-05</v>
+        <v>0.086989626288414</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001888346741907299</v>
+        <v>0.1165915578603745</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0006081914762035012</v>
+        <v>0.0279095433652401</v>
       </c>
       <c r="FP5" t="n">
-        <v>4.105435800738633e-05</v>
+        <v>0.1068884879350662</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0004360717721283436</v>
+        <v>0.05266369506716728</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001649515586905181</v>
+        <v>0.08890077471733093</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0004063196538481861</v>
+        <v>0.1841214001178741</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0005219239392317832</v>
+        <v>0.2633685171604156</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0007297386764548719</v>
+        <v>0.3927189111709595</v>
       </c>
       <c r="FV5" t="n">
-        <v>3.608522820286453e-05</v>
+        <v>0.00385834276676178</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0002062801067950204</v>
+        <v>0.0178244411945343</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0003450915100984275</v>
+        <v>0.1580028831958771</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0002207907091360539</v>
+        <v>0.1232680380344391</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.000351100810803473</v>
+        <v>0.08477962017059326</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0005498326499946415</v>
+        <v>0.1199363023042679</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0002321362117072567</v>
+        <v>0.1008632928133011</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001652986858971417</v>
+        <v>0.1888724565505981</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0005270119872875512</v>
+        <v>0.1526010036468506</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0006021971930749714</v>
+        <v>0.1390141248703003</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0001808807428460568</v>
+        <v>0.1901597380638123</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0001348248188151047</v>
+        <v>0.1512298583984375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9.500030500930734e-06</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7.462772919097915e-05</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.487089897040278e-05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.448109055170789e-05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.112276095227571e-05</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0001080069851013832</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.048962894856231e-05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.11496585002169e-05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.89673441532068e-05</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.471127340366365e-06</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.877355139702559e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001108087017200887</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.430962856829865e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.58150971098803e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8.036413055378944e-05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.058730832592119e-06</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.268413512269035e-05</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.284620369318873e-05</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.167046775663039e-05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.354991688160226e-06</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.747509931097738e-06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.649154000915587e-06</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.621740011614747e-05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.015758557012305e-05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.598552423994988e-06</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.417253381281625e-05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.846454652986722e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.046577174041886e-05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.650709418754559e-05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.602629822627932e-06</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.049279257538728e-05</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.009652623906732e-05</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7.10987933416618e-06</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.123147103498923e-05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.255644474440487e-05</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5.200184023124166e-05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.267226252821274e-05</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4.248967888997868e-05</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.627158053452149e-05</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.228817563969642e-05</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4.221039853291586e-05</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.955888728844002e-05</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.209931269841036e-05</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.183771125099156e-06</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.99867575551616e-06</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.311626980779693e-06</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.0001182230553240515</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.39447376265889e-06</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.40713915345259e-06</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.669924288056791e-05</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.0001014862355077639</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.004177415277809e-05</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.592299279058352e-05</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.312225842615589e-05</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.500222763046622e-05</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.076852514524944e-05</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.920543142361566e-05</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.266586984158494e-06</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.186176061513834e-05</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>5.065688583272276e-06</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.065819171548355e-05</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9.477584171690978e-06</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.399506163579645e-05</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.68815840879688e-05</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9.647399565437809e-06</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2.734003464865964e-05</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.014768117282074e-05</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.219902060256572e-06</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>4.656699729821412e-06</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>3.162249413435347e-05</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.546947714814451e-05</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1.399771463184152e-06</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.724465073493775e-05</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>4.433303183759563e-05</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.076038461178541e-05</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>8.066389455052558e-06</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.249434262717841e-05</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>7.358439324889332e-05</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.963599061127752e-05</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2.662180850165896e-05</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1.014473127725068e-07</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.309990122739691e-06</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>2.878529994632117e-05</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>2.095800300594419e-05</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>3.995189217675943e-06</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1.687549683992984e-06</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>2.542566289776005e-05</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>3.507005885694525e-06</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.365913135487062e-06</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>6.211076652107295e-06</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>3.711364479386248e-05</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>2.192924148403108e-05</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>3.01186755677918e-05</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>3.597042450564913e-05</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>2.701580160646699e-05</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>5.025187419960275e-05</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>1.431865894119255e-05</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>1.310785137320636e-05</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>4.253585643709812e-07</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>8.793062988843303e-07</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>3.505122731439769e-05</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>2.699442848097533e-05</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>3.469484909146558e-06</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>8.18333683128003e-06</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>3.044420373043977e-05</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>4.99046063850983e-06</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>2.675621090020286e-06</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>2.588760708022164e-07</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>1.762214560585562e-05</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>7.118945359252393e-05</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>5.632684406009503e-06</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>6.00377006776398e-06</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>6.272384780459106e-05</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>4.255896419635974e-05</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>1.036074263538467e-05</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>4.274234743206762e-05</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>3.958144134230679e-06</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>9.7520451163291e-06</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1.253520713362377e-05</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>1.697521838650573e-05</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>8.747115316509735e-06</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>1.682445326878224e-05</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>8.909332791517954e-06</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>1.701129008324642e-06</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>2.870869684556965e-05</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>4.934194748784648e-06</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>5.714864528272301e-06</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>4.554469705908559e-05</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>1.246840292878915e-05</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>1.632414750929456e-06</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>2.37031708820723e-05</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>4.763829929288477e-05</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>5.929529152126634e-07</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>2.186708843510132e-05</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>8.806205187283922e-08</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>7.096607532730559e-06</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>2.694788781809621e-05</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>2.325337118236348e-05</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>1.384730967401993e-05</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>6.004491751809837e-06</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>2.03553213395935e-06</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>1.626706762181129e-05</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>8.279253961518407e-06</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>1.396637117068167e-06</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>1.355859421892092e-05</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>1.7082056729123e-05</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>1.285136022488587e-06</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>1.922751107485965e-05</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>9.211884389515035e-06</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>1.239309040101944e-05</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>3.046955271202023e-06</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>2.2235148207983e-05</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>2.272045094287023e-05</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>3.455066234892001e-06</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>3.36674929712899e-05</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>2.012497861869633e-05</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>1.815819814510178e-06</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>4.016041657450842e-06</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>3.177884718752466e-05</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>2.73191881206003e-06</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>1.763205546012614e-07</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>4.587606781569775e-06</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>3.719830601767171e-06</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>1.985804192372598e-05</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>5.732683348469436e-06</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>1.333550426352303e-05</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>3.062716132262722e-05</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>6.462952114816289e-06</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>1.921343709909706e-06</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>5.751035558887452e-08</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>1.108466949517606e-05</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>2.565519025665708e-05</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>9.754283382790163e-06</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>6.521691375382943e-06</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>6.018325075274333e-05</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>6.523031515826005e-06</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>7.08534280420281e-05</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>4.456504757399671e-05</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>1.007217542792205e-05</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>2.697798117878847e-05</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>2.360779399168678e-05</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>3.786876186495647e-05</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>3.179360646754503e-05</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>1.368023549730424e-05</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>8.113527655950747e-06</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>1.116155726776924e-05</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>5.556055839406326e-06</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>2.815635889419354e-05</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>1.560205419082195e-05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.03442076221108437</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1922491490840912</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03390286862850189</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.004790935665369034</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1170700043439865</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2176487743854523</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.03485154360532761</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1788011789321899</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0620434507727623</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01762653142213821</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.280599057674408</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.08717391639947891</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.06686067581176758</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2392973750829697</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2592820823192596</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.01521723810583353</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.107318639755249</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.06626902520656586</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01178954727947712</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.072379469871521</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.03614981099963188</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.09892605245113373</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.08844089508056641</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04249726980924606</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01847896352410316</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.04513205587863922</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.001979548949748278</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02551671303808689</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.005595277063548565</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.0001656999811530113</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.009272727183997631</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09149682521820068</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.08120184391736984</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.001536373980343342</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0410952977836132</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.01220805570483208</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.005804397165775299</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.05019677802920341</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.01348681375384331</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.03606114909052849</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.02866566367447376</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.04433242231607437</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.01984910294413567</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.05889922752976418</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.005223354324698448</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.02790830098092556</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.4257031679153442</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.01754235662519932</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.02118178270757198</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.006790041923522949</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.166816234588623</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.02845217287540436</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.03661231324076653</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.006503930315375328</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.01023282296955585</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.1054282784461975</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.007112191058695316</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.03499413281679153</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.08261029422283173</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.04022140428423882</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.01433034799993038</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.04323793202638626</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.01342788059264421</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.008281132206320763</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.09730057418346405</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.08746536821126938</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.005017188377678394</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.0790434405207634</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.02407239750027657</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.06773240119218826</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.04655759036540985</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.04142176359891891</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.0355839692056179</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.2321446537971497</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.002232963219285011</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.1174440979957581</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.05477876961231232</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.08251155912876129</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.02850648947060108</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.04711603745818138</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.001307411468587816</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.005097460001707077</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.05997847020626068</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.02548755705356598</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.002198773436248302</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.03374597802758217</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.05815786868333817</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.02583526261150837</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.004887592978775501</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.007048303261399269</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.06113275140523911</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.1775852739810944</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.02238381654024124</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.05292330682277679</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.02719327248632908</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.06585478782653809</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.01177588477730751</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.08621351420879364</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.03387495130300522</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.01317527052015066</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.04621633514761925</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.03255351260304451</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.01385598909109831</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.03056566044688225</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.06699071824550629</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.01663810014724731</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.0100796902552247</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.007773608900606632</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.03159851580858231</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.08118092268705368</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.0208921916782856</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.008183619007468224</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.04016482830047607</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.03305690363049507</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.01381388586014509</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.07606669515371323</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.04014772921800613</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.05439354479312897</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.04882365092635155</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.009919429197907448</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.04706307873129845</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.0189647264778614</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.01272779330611229</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.0197707861661911</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.01598859205842018</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.04711634665727615</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.04919636994600296</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.08138976991176605</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.05192918330430984</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.01100007258355618</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.04496254771947861</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.06584446877241135</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.004266343079507351</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.0002160529838874936</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.04191841185092926</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.01739161275327206</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.013237533159554</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.003942635841667652</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.01832695119082928</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.01567753404378891</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.01921896263957024</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.01273294538259506</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.02619747258722782</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.00216739485040307</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.003348054364323616</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.04781017452478409</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.01071114931255579</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.01461025606840849</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.01399461925029755</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.03943566977977753</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.01082236133515835</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.02575943619012833</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.03057081624865532</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.002629893831908703</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.07254740595817566</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.01759576424956322</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.007412325590848923</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.01969866827130318</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.06430468708276749</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.03603362664580345</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.009415959939360619</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.0001678646076470613</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.01166318263858557</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.04158660769462585</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.02380825765430927</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.0666273906826973</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.007134630344808102</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.01585492491722107</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.04369750991463661</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.03196613118052483</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.05730167031288147</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.004569863900542259</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.06879745423793793</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.03775440156459808</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.07348662614822388</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.03061198070645332</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.04862859845161438</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.009004101157188416</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.0977008193731308</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.04725708812475204</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.006070545874536037</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.02463998273015022</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.03478816896677017</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.009211655706167221</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.002690829336643219</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.01197798736393452</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.04323264583945274</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.003152952063828707</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.008909040130674839</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6.554111314471811e-05</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001920601353049278</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.362145071150735e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.66118001693394e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.519960253266618e-05</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00012260174844414</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.909216608619317e-06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001137792569352314</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.607931153557729e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.574719085008837e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002489550970494747</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.079774564364925e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001155947102233768</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.723624078906141e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0001126827628468163</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6.624722300330177e-05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.586881565657677e-06</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.16284310631454e-05</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.956437467422802e-06</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.420939538045786e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8.258688467321917e-06</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.966605436289683e-05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.229751771665178e-05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>8.293480277643539e-06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.110666537191719e-05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.263381000171648e-05</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.178632282972103e-05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.503637006157078e-05</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.562279016477987e-05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.030327075568493e-05</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>6.128550739958882e-05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>5.86149180890061e-05</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.601631538505899e-06</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.891577085189056e-05</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9.084319026442245e-05</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.891988540592138e-05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>8.278717359644361e-06</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.62262362614274e-05</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.331987732555717e-05</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.769799928297289e-05</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>4.059991169924615e-06</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.28778694185894e-05</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.020658136345446e-05</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.69628313719295e-05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.0344747150084e-06</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.093505438300781e-05</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.0002205178025178611</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.378363387833815e-05</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.874022902688012e-05</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.675866411067545e-05</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.0001240554265677929</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.046605343115516e-06</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.512756954180077e-06</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2.277516068716068e-05</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.639696893107612e-05</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.180466592311859e-06</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.876560236269142e-05</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.775203367695212e-05</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.079629146261141e-05</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1.256823179573985e-05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.162051482126117e-06</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>6.027604467817582e-05</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.279569733014796e-05</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>6.28249290457461e-06</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>6.307013973128051e-05</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>2.5896666556946e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.05955018120585e-06</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>4.328059731051326e-05</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.607380909263156e-05</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>7.245424785651267e-05</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>5.935093213338405e-06</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>2.178129216190428e-05</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>2.675938958418556e-06</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.0001279444841202348</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.54561876115622e-05</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>7.807258953107521e-06</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.399564982624725e-05</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>4.69128972326871e-05</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>4.19587959186174e-05</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>9.192533980240114e-06</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>1.066264485416468e-05</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>9.707378012535628e-07</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>6.285166455199942e-05</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>3.635739631135948e-06</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>3.756202659133123e-06</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1.102185342460871e-05</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>2.599407162051648e-05</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>5.060598596173804e-06</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.300197800446767e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>6.821684337410261e-07</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>6.595419836230576e-05</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0001204444415634498</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>2.588566712802276e-05</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>5.148883064975962e-05</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>4.696770702139474e-05</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>3.011909029737581e-05</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>7.672591891605407e-06</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>3.67536922567524e-05</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>2.015792233578395e-05</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1.276711373066064e-05</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>6.271777237998322e-05</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.243395490746479e-05</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1.302598775509978e-05</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>5.745519501942908e-06</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>2.749663690337911e-05</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>7.080044269969221e-06</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>8.865785275702365e-06</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3.283088062744355e-06</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>5.184059318708023e-06</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>5.960814087302424e-05</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>2.979380769829731e-05</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>5.588838757830672e-05</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>6.334306817734614e-06</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>5.571135625359602e-05</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>1.3605574167741e-05</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>8.783923476585187e-06</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>3.30934017256368e-06</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>5.188845534576103e-05</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>3.879420910379849e-05</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>1.873489600257017e-05</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>5.749056435888633e-05</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>1.055091706803069e-05</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>1.735028490656987e-06</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>7.62659874453675e-06</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>2.48313881456852e-06</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>4.841992267756723e-05</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>4.470246494747698e-05</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>4.335688572609797e-05</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>1.066772892954759e-05</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>3.597597697080346e-06</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>3.300203752587549e-05</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>1.056977271218784e-05</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>6.639844741584966e-06</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>2.815600964822806e-05</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>4.383995474199764e-05</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>3.555084731488023e-06</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>1.985669587156735e-05</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>3.003241545229685e-06</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>4.638328027795069e-05</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>4.077887933817692e-05</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>1.744863584463019e-05</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>8.648163202451542e-06</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>1.153675202658633e-05</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>3.878550160152372e-06</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>1.347391298622824e-05</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>1.644831718294881e-05</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>9.162249625660479e-06</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>1.919214810186531e-05</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>1.949779652932193e-05</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>2.4825027139741e-05</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>2.37345147979795e-07</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>1.592550870554987e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>3.191340738339932e-06</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>6.240734364837408e-06</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>6.929481605766341e-05</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>1.547432475490496e-06</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>5.397022960096365e-06</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>2.900640083680628e-06</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>2.353158379264642e-05</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>6.56748443361721e-06</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>7.942014235595707e-06</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>6.660681719949935e-06</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>9.481746019446291e-06</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>3.352186831762083e-05</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>2.525224408600479e-05</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>3.579580152290873e-05</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>2.895179386541713e-05</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>4.929523129248992e-05</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>2.240930371044669e-05</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>3.043935066671111e-05</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>7.809924136381596e-05</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>2.976557880174369e-05</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>5.893517663935199e-05</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>6.153751019155607e-05</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>4.719410208053887e-05</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>4.849977631238289e-05</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>1.101786983781494e-05</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>3.15198085445445e-05</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>4.998711301595904e-05</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>5.697225788026117e-05</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>1.051470280799549e-05</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>1.826485458877869e-05</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>5.639123264700174e-05</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>9.267494533560239e-06</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>5.870580935152248e-05</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>4.649415132007562e-06</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>5.046306250733323e-05</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>1.528735265310388e-05</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>9.988254532800056e-06</v>
       </c>
     </row>
   </sheetData>
